--- a/dataset/v2/eni_progress.xlsx
+++ b/dataset/v2/eni_progress.xlsx
@@ -569,12 +569,17 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Workshop</t>
+          <t>Manifold</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>03/Aug/2026</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>06/Aug/2026</t>
         </is>
       </c>
       <c r="I5" t="n">
@@ -612,17 +617,12 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Unit 2</t>
+          <t>Tank Farm</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>07/08/2026</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
+          <t>07/Aug/2026</t>
         </is>
       </c>
       <c r="I6" t="n">
@@ -635,12 +635,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>EL-CBL-1376</t>
+          <t>EL-CBL-1377</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>P-1401A</t>
+          <t>WHCP-2101</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -650,7 +650,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Pull LV power cables, pump motors P-1401A/B</t>
+          <t>Pull LV power cables, wellhead panel WHCP-2101 feeders, Unit 2</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -660,35 +660,35 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Workshop</t>
+          <t>Tank Farm</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>25/Jul/2026</t>
+          <t>08/Jul/2026</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>30/Jul/2026</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="I7" t="n">
-        <v>320</v>
+        <v>260</v>
       </c>
       <c r="J7" t="n">
-        <v>320</v>
+        <v>260</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>EL-CBL-1377</t>
+          <t>EL-CBL-1382</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>WHCP-2101</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -698,7 +698,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Pull LV power cables, wellhead panel WHCP-2101 feeders, Unit 2</t>
+          <t>Glanding and termination, LV panels, substation</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -706,21 +706,26 @@
           <t>ELE</t>
         </is>
       </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Tank Farm</t>
+        </is>
+      </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>01/08/2026</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>11/07/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
       <c r="I8" t="n">
-        <v>260</v>
+        <v>84</v>
       </c>
       <c r="J8" t="n">
-        <v>260</v>
+        <v>84</v>
       </c>
     </row>
     <row r="9">
@@ -751,17 +756,12 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Manifold</t>
+          <t>Tank Farm</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>03/Aug/2026</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>05/08/2026</t>
+          <t>03/08/2026</t>
         </is>
       </c>
       <c r="I9" t="n">
@@ -847,17 +847,17 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tank Farm</t>
+          <t>Substation</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>25/09/2026</t>
+          <t>25/Sep/2026</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>28/09/2026</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="I11" t="n">
@@ -893,14 +893,9 @@
           <t>ELE</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Unit 2</t>
-        </is>
-      </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>29/09/2026</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -918,7 +913,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>EL-GRD-1378</t>
+          <t>EL-ENS-1532</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -933,7 +928,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Earth grid and earthing pits, site-wide</t>
+          <t>Substation energization</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -943,30 +938,24 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tank Farm</t>
+          <t>Unit 2</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
-        <v>2400</v>
-      </c>
-      <c r="J13" t="n">
-        <v>2400</v>
+          <t>12/Oct/2026</t>
+        </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>EL-GRD-1379</t>
+          <t>EL-GRD-1378</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -981,7 +970,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Lightning mast and down conductors, flare area</t>
+          <t>Earth grid and earthing pits, site-wide</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -991,30 +980,25 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Workshop</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>05/May/2026</t>
+          <t>Tank Farm</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>07/May/2026</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="I14" t="n">
-        <v>4</v>
+        <v>2400</v>
       </c>
       <c r="J14" t="n">
-        <v>4</v>
+        <v>2400</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>EL-LTG-1381</t>
+          <t>EL-SWB-1373</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1029,7 +1013,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Emergency lighting and exit signage, control building</t>
+          <t>Install MCC panels and switchboard, substation room</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1039,35 +1023,35 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Unit 1</t>
+          <t>Substation</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>20/Jul/2026</t>
+          <t>11/07/2026</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>17/07/2026</t>
         </is>
       </c>
       <c r="I15" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="J15" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>EL-SWB-1373</t>
+          <t>EL-TRF-1372</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>T-2</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1077,7 +1061,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Install MCC panels and switchboard, substation room</t>
+          <t>Set and terminate transformer T-2, 11/0.433 kV</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1085,32 +1069,27 @@
           <t>ELE</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Unit 2</t>
-        </is>
-      </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>17/Jul/2026</t>
+          <t>05/08/2026</t>
         </is>
       </c>
       <c r="I16" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="J16" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>EL-TRK-1361</t>
+          <t>EL-TRK-1360</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1125,7 +1104,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Install cable tray 450 mm, rack tier 3, Unit 2 stretch</t>
+          <t>Install cable tray ladder 600 mm, rack tier 3</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1135,30 +1114,30 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Unit 1</t>
+          <t>Manifold</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>07/Jul/2026</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="I17" t="n">
-        <v>140</v>
+        <v>210</v>
       </c>
       <c r="J17" t="n">
-        <v>140</v>
+        <v>210</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>EL-TRK-1370</t>
+          <t>EL-TRK-1361</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1173,7 +1152,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Install cable tray and risers, substation building</t>
+          <t>Install cable tray 450 mm, rack tier 3, Unit 2 stretch</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1183,30 +1162,35 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Unit 2</t>
+          <t>Manifold</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>03/07/2026</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="I18" t="n">
-        <v>120</v>
+        <v>140</v>
       </c>
       <c r="J18" t="n">
-        <v>120</v>
+        <v>140</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>INS-CBL-1396</t>
+          <t>EL-TRK-1362</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>JB-101</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1216,45 +1200,40 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Pull instrument cables, rack tier 2 to junction boxes JB-101 to JB-108</t>
+          <t>Install conduits and flexible connections, Unit 1/2 equipment</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>INS</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Substation</t>
+          <t>ELE</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>28/Aug/2026</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="I19" t="n">
-        <v>640</v>
+        <v>38</v>
       </c>
       <c r="J19" t="n">
-        <v>640</v>
+        <v>38</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>INS-CHK-1406</t>
+          <t>INS-CBL-1396</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>JB-101</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1264,7 +1243,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Loop check, Unit 1 loops L-1101 to L-1128</t>
+          <t>Pull instrument cables, rack tier 2 to junction boxes JB-101 to JB-108</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1274,30 +1253,30 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tank Farm</t>
+          <t>Unit 1</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>15/12/2026</t>
+          <t>28/Aug/2026</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>19/Dec/2026</t>
+          <t>03/Sep/2026</t>
         </is>
       </c>
       <c r="I20" t="n">
-        <v>28</v>
+        <v>640</v>
       </c>
       <c r="J20" t="n">
-        <v>28</v>
+        <v>640</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>INS-CHK-1408</t>
+          <t>INS-CHK-1406</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1312,7 +1291,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Loop check, tank farm and utilities loops</t>
+          <t>Loop check, Unit 1 loops L-1101 to L-1128</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1322,30 +1301,30 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Workshop</t>
+          <t>Unit 1</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>13/Nov/2026</t>
+          <t>15/Dec/2026</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>16/Nov/2026</t>
+          <t>19/12/2026</t>
         </is>
       </c>
       <c r="I21" t="n">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="J21" t="n">
-        <v>16</v>
+        <v>28</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>INS-CHK-1540</t>
+          <t>INS-CHK-1407</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1360,7 +1339,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Revalidation of loop checks, post hydrotest</t>
+          <t>Loop check, Unit 2 loops L-2101 to L-2122</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1370,35 +1349,35 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Substation</t>
+          <t>Manifold</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>2026-11-15</t>
+          <t>07/11/2026</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2026-11-17</t>
+          <t>11/Nov/2026</t>
         </is>
       </c>
       <c r="I22" t="n">
-        <v>66</v>
+        <v>22</v>
       </c>
       <c r="J22" t="n">
-        <v>66</v>
+        <v>22</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>INS-FIT-1391</t>
+          <t>INS-CHK-1408</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>PT-1101</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1408,7 +1387,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Install pressure transmitters PT-1101 to PT-1114, Unit 1</t>
+          <t>Loop check, tank farm and utilities loops</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1418,35 +1397,30 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Unit 1</t>
+          <t>Tank Farm</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>2026-11-30</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>2026-12-04</t>
+          <t>13/11/2026</t>
         </is>
       </c>
       <c r="I23" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="J23" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>INS-FIT-1392</t>
+          <t>INS-CHK-1542</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>LT-1201</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1456,7 +1430,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Install level transmitters LT-1201 to LT-1206, separators</t>
+          <t>Integrated ESD and blowdown function test</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1466,30 +1440,30 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Manifold</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>17/Jun/2026</t>
+          <t>Workshop</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>2027-01-03</t>
         </is>
       </c>
       <c r="I24" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J24" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>INS-FIT-1393</t>
+          <t>INS-FIT-1392</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>TE-1301</t>
+          <t>LT-1201</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1499,7 +1473,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Install temperature elements TE-1301 to TE-1312</t>
+          <t>Install level transmitters LT-1201 to LT-1206, separators</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1514,30 +1488,30 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>03/Nov/2026</t>
+          <t>20/Jun/2026</t>
         </is>
       </c>
       <c r="I25" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="J25" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>INS-FIT-1394</t>
+          <t>INS-FIT-1393</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>FE-1401</t>
+          <t>TE-1301</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1547,7 +1521,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Install flow meter elements FE-1401 to FE-1408, Unit 2</t>
+          <t>Install temperature elements TE-1301 to TE-1312</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1557,35 +1531,25 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Unit 2</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>02/11/2026</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>2026-11-05</t>
+          <t>Substation</t>
         </is>
       </c>
       <c r="I26" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="J26" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>INS-FIT-1400</t>
+          <t>INS-FIT-1394</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>FE-1401</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1595,7 +1559,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Install fire and gas detectors, wellhead and manifold</t>
+          <t>Install flow meter elements FE-1401 to FE-1408, Unit 2</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1603,37 +1567,32 @@
           <t>INS</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>Unit 1</t>
-        </is>
-      </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>30/11/2026</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2026-12-04</t>
+          <t>05/11/2026</t>
         </is>
       </c>
       <c r="I27" t="n">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="J27" t="n">
-        <v>32</v>
+        <v>8</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>INS-IMP-1399</t>
+          <t>INS-JBX-1395</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>JB-101</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1643,7 +1602,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Install ESD valve solenoids and actuation hook-up, blowdown headers 6"</t>
+          <t>Install junction boxes JB-101 to JB-108, field</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1651,32 +1610,27 @@
           <t>INS</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>Manifold</t>
-        </is>
-      </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>18/11/2026</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>21/11/2026</t>
+          <t>27/08/2026</t>
         </is>
       </c>
       <c r="I28" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J28" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>INS-JBX-1395</t>
+          <t>INS-TER-1398</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1691,7 +1645,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Install junction boxes JB-101 to JB-108, field</t>
+          <t>Terminate field instruments at JB-101 to JB-108</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1701,35 +1655,35 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Unit 1</t>
+          <t>Workshop</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>24/08/2026</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>27/Aug/2026</t>
+          <t>18/Sep/2026</t>
         </is>
       </c>
       <c r="I29" t="n">
-        <v>8</v>
+        <v>168</v>
       </c>
       <c r="J29" t="n">
-        <v>8</v>
+        <v>168</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>INS-TER-1398</t>
+          <t>INS-TRK-1363</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>JB-101</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1739,7 +1693,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Terminate field instruments at JB-101 to JB-108</t>
+          <t>Install instrument cable tray 300 mm, rack tier 2</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1749,24 +1703,19 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tank Farm</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
+          <t>Unit 2</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>10/Jul/2026</t>
         </is>
       </c>
       <c r="I30" t="n">
-        <v>168</v>
+        <v>180</v>
       </c>
       <c r="J30" t="n">
-        <v>168</v>
+        <v>180</v>
       </c>
     </row>
     <row r="31">
